--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB SALLIVER FUENGIROLA HIGUERÓN HOTEL.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB SALLIVER FUENGIROLA HIGUERÓN HOTEL.xlsx
@@ -565,13 +565,13 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>17.4545</v>
+        <v>20.7958</v>
       </c>
       <c r="E2" t="n">
-        <v>12.6835</v>
+        <v>18.7293</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7714</v>
+        <v>2.0667</v>
       </c>
       <c r="G2" t="n">
         <v>7.709199999999999</v>
@@ -610,13 +610,13 @@
         <v>28.7426</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6087000000000002</v>
+        <v>2.7325</v>
       </c>
       <c r="T2" t="n">
-        <v>-8.737500000000001</v>
+        <v>-2.6918</v>
       </c>
       <c r="U2" t="n">
-        <v>8.1287</v>
+        <v>5.4242</v>
       </c>
       <c r="V2" t="n">
         <v>2.029</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. TERRÓN FERNÁNDEZ</t>
+          <t>A. MARTIN ALCAINE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8535</v>
+        <v>9.3126</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8535</v>
+        <v>4.6983</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4.6143</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8535</v>
+        <v>2.896</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2374</v>
+        <v>-1.5257</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6161</v>
+        <v>4.4216</v>
       </c>
       <c r="J3" t="n">
-        <v>7.8535</v>
+        <v>1.9434</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2374</v>
+        <v>-0.8198</v>
       </c>
       <c r="L3" t="n">
-        <v>3.6161</v>
+        <v>2.7632</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.9525</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.7058</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.6584</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>4.3609</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.7978</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.8492</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.9485</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.2402</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.8879</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.6477</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MARTIN ALCAINE</t>
+          <t>D. TERRÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>7.100099999999999</v>
+        <v>7.8535</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3281</v>
+        <v>7.8535</v>
       </c>
       <c r="F4" t="n">
-        <v>3.772</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.896</v>
+        <v>7.8535</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5257</v>
+        <v>4.2374</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4216</v>
+        <v>3.6161</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9434</v>
+        <v>7.8535</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8198</v>
+        <v>4.2374</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7632</v>
+        <v>3.6161</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9525</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7058</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6584</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>4.3609</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4147000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5208999999999999</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1062</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2.2402</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.8879</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MOLPECERES ALCELAY</t>
+          <t>J. LUQUE GOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.976</v>
+        <v>2.435299999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.3404</v>
+        <v>-1.0163</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6356000000000001</v>
+        <v>3.4515</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3029</v>
+        <v>9.183400000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4936</v>
+        <v>-0.5146999999999997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8093</v>
+        <v>9.698</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9749</v>
+        <v>21.9345</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2958</v>
+        <v>7.31</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6791</v>
+        <v>14.6247</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.328</v>
+        <v>-12.7513</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1979</v>
+        <v>-7.8246</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1301</v>
+        <v>-4.9267</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7929</v>
+        <v>-2.3788</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>-25.9671</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1982</v>
+        <v>23.5886</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8802</v>
+        <v>-7.0029</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3744</v>
+        <v>-4.015000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5059</v>
+        <v>-2.9881</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.6335</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>7.031499999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-4.398</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.0822</v>
+        <v>-2.7767</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.5034</v>
+        <v>-3.1978</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4210999999999999</v>
+        <v>0.4212</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2689</v>
@@ -922,10 +922,10 @@
         <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5029</v>
+        <v>-0.1973</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2386</v>
+        <v>0.06709999999999999</v>
       </c>
       <c r="U6" t="n">
         <v>-0.2644</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GONZALEZ GUISADO</t>
+          <t>M. MOLPECERES ALCELAY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3691</v>
+        <v>-2.818</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1491</v>
+        <v>-2.2385</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.22</v>
+        <v>-0.5795</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9607000000000001</v>
+        <v>-1.3029</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06289999999999996</v>
+        <v>-0.4936</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0236</v>
+        <v>-0.8093</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1613</v>
+        <v>-0.9749</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1211</v>
+        <v>-0.2958</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0402</v>
+        <v>-0.6791</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1219</v>
+        <v>-0.328</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05809999999999993</v>
+        <v>-0.1979</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0638</v>
+        <v>-0.1301</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1894</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01200000000000001</v>
+        <v>-0.7222</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6718</v>
+        <v>-0.2725</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6839000000000001</v>
+        <v>-0.4497</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.1714</v>
+        <v>-3.601300000000002</v>
       </c>
       <c r="E8" t="n">
-        <v>-17.15</v>
+        <v>-15.064</v>
       </c>
       <c r="F8" t="n">
-        <v>12.9783</v>
+        <v>11.4629</v>
       </c>
       <c r="G8" t="n">
         <v>-6.476100000000001</v>
@@ -1078,13 +1078,13 @@
         <v>51.9345</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2787</v>
+        <v>-0.7087000000000004</v>
       </c>
       <c r="T8" t="n">
-        <v>-4.085</v>
+        <v>-1.999</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8058</v>
+        <v>1.2902</v>
       </c>
       <c r="V8" t="n">
         <v>9.728399999999999</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. QUINTANILLA GARRIDO</t>
+          <t>M. GONZALEZ GUISADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.3262</v>
+        <v>-3.6819</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5789</v>
+        <v>-1.6585</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.7473</v>
+        <v>-2.0234</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0732</v>
+        <v>-0.9607000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1191</v>
+        <v>0.06289999999999996</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0459</v>
+        <v>-1.0236</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2758</v>
+        <v>0.1613</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3159</v>
+        <v>0.1211</v>
       </c>
       <c r="L9" t="n">
         <v>0.0402</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7975</v>
+        <v>-1.1219</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8032</v>
+        <v>-0.05809999999999993</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0057</v>
+        <v>-1.0638</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5947</v>
+        <v>-1.1894</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3964</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.244</v>
+        <v>-0.3249000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.312</v>
+        <v>0.1626</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9321</v>
+        <v>-0.4873</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4142</v>
+        <v>-1.2071</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4142</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LIBERATORE DARGAM</t>
+          <t>V. QUINTANILLA GARRIDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9708</v>
+        <v>-5.2981</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5908</v>
+        <v>-1.5789</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3801</v>
+        <v>-3.7192</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3288</v>
+        <v>-1.0732</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5661</v>
+        <v>-1.1191</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8949</v>
+        <v>0.0459</v>
       </c>
       <c r="J10" t="n">
-        <v>3.312400000000001</v>
+        <v>-0.2758</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2833</v>
+        <v>-0.3159</v>
       </c>
       <c r="L10" t="n">
-        <v>4.5959</v>
+        <v>0.0402</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9836000000000001</v>
+        <v>-0.7975</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2827</v>
+        <v>-0.8032</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7009000000000001</v>
+        <v>0.0057</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.9466</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-10.1093</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>4.1628</v>
+        <v>0.3964</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9976</v>
+        <v>-1.216</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9991</v>
+        <v>-0.312</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9985000000000001</v>
+        <v>-0.904</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.3507</v>
+        <v>-2.4142</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.5578</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LUQUE GOMEZ</t>
+          <t>J. HERMOSO PINO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0025</v>
+        <v>-6.0795</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6318</v>
+        <v>-3.1146</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6291000000000002</v>
+        <v>-2.9649</v>
       </c>
       <c r="G11" t="n">
-        <v>9.183400000000001</v>
+        <v>-2.8873</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5146999999999997</v>
+        <v>-2.4415</v>
       </c>
       <c r="I11" t="n">
-        <v>9.698</v>
+        <v>-0.4458</v>
       </c>
       <c r="J11" t="n">
-        <v>21.9345</v>
+        <v>-0.4172</v>
       </c>
       <c r="K11" t="n">
-        <v>7.31</v>
+        <v>-0.4975000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>14.6247</v>
+        <v>0.0804</v>
       </c>
       <c r="M11" t="n">
-        <v>-12.7513</v>
+        <v>-2.4701</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.8246</v>
+        <v>-1.9439</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.9267</v>
+        <v>-0.5262</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3788</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q11" t="n">
-        <v>-25.9671</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>23.5886</v>
+        <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>-15.4408</v>
+        <v>-0.9167</v>
       </c>
       <c r="T11" t="n">
-        <v>-9.6305</v>
+        <v>-0.9818</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.8102</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>2.6335</v>
+        <v>-2.0773</v>
       </c>
       <c r="W11" t="n">
-        <v>7.031499999999999</v>
+        <v>0.2666</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.398</v>
+        <v>-2.3438</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. HERMOSO PINO</t>
+          <t>J. GARCIA RAMOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0867</v>
+        <v>-6.091099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3184</v>
+        <v>-4.7184</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7683</v>
+        <v>-1.3727</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8873</v>
+        <v>-3.3963</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4415</v>
+        <v>-1.7949</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4458</v>
+        <v>-1.6014</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4172</v>
+        <v>-2.1211</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4975000000000001</v>
+        <v>-0.2081000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0804</v>
+        <v>-1.913</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.4701</v>
+        <v>-1.2752</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.9439</v>
+        <v>-1.5867</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5262</v>
+        <v>0.3115</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1982</v>
+        <v>0.5947000000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R12" t="n">
-        <v>1.784</v>
+        <v>2.5769</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.924</v>
+        <v>-3.3569</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1856</v>
+        <v>-0.8817</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2616000000000001</v>
+        <v>-2.4753</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.0773</v>
+        <v>0.0674</v>
       </c>
       <c r="W12" t="n">
         <v>0.2666</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3438</v>
+        <v>-0.1992</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. GARCIA RAMOS</t>
+          <t>M. LIBERATORE DARGAM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.672499999999999</v>
+        <v>-6.3277</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.8225</v>
+        <v>-5.1396</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.85</v>
+        <v>-1.188</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.3963</v>
+        <v>2.3288</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7949</v>
+        <v>-1.5661</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6014</v>
+        <v>3.8949</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1211</v>
+        <v>3.312400000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2081000000000001</v>
+        <v>-1.2833</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.913</v>
+        <v>4.5959</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2752</v>
+        <v>-0.9836000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5867</v>
+        <v>-0.2827</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3115</v>
+        <v>-0.7009000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5947000000000001</v>
+        <v>-5.9466</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9822</v>
+        <v>-10.1093</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5769</v>
+        <v>4.1628</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.9383</v>
+        <v>1.6408</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9856</v>
+        <v>0.4502</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.9527</v>
+        <v>1.1905</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0674</v>
+        <v>-4.3507</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1992</v>
+        <v>-5.5578</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. MORENO VEGA</t>
+          <t>D. GUERRERO JONSSON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.2089</v>
+        <v>-9.745100000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.228999999999999</v>
+        <v>-7.870699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9799000000000004</v>
+        <v>-1.8745</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.5787</v>
+        <v>-4.694100000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.753</v>
+        <v>-1.1622</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.8258</v>
+        <v>-3.5319</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.2311</v>
+        <v>-2.5294</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4899999999999999</v>
+        <v>-0.8135000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.7412</v>
+        <v>-1.716</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.3476</v>
+        <v>-2.1646</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.2631</v>
+        <v>-0.3488</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.08460000000000001</v>
+        <v>-1.8159</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-0.1983999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.9555</v>
+        <v>-5.3519</v>
       </c>
       <c r="R14" t="n">
-        <v>4.9555</v>
+        <v>5.1538</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.0468</v>
+        <v>-4.1205</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0421</v>
+        <v>-1.1962</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.0046</v>
+        <v>-2.9243</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5834999999999999</v>
+        <v>-0.7323</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5834999999999999</v>
+        <v>-1.9394</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. GUERRERO JONSSON</t>
+          <t>G. CABRERA RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>-10.8952</v>
+        <v>-9.831399999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.402899999999999</v>
+        <v>-8.6356</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4923</v>
+        <v>-1.196</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.694100000000001</v>
+        <v>-10.7482</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1622</v>
+        <v>-5.7829</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.5319</v>
+        <v>-4.9652</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.5294</v>
+        <v>-3.878400000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8135000000000001</v>
+        <v>-1.8605</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.716</v>
+        <v>-2.0179</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1646</v>
+        <v>-6.8697</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3488</v>
+        <v>-3.9226</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8159</v>
+        <v>-2.9473</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1983999999999999</v>
+        <v>6.3431</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.3519</v>
+        <v>-6.1448</v>
       </c>
       <c r="R15" t="n">
-        <v>5.1538</v>
+        <v>12.488</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.2704</v>
+        <v>-5.0674</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.7285</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.5419</v>
+        <v>-4.1818</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7323</v>
+        <v>-0.3591</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2071</v>
+        <v>2.2734</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.9394</v>
+        <v>-2.6325</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. NARANJO FERNANDEZ</t>
+          <t>P. MORENO VEGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.2336</v>
+        <v>-9.903300000000002</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.9849</v>
+        <v>-8.923300000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.2487</v>
+        <v>-0.9801000000000002</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.0186</v>
+        <v>-6.5787</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7579</v>
+        <v>-3.753</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.2607</v>
+        <v>-2.8258</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.1965</v>
+        <v>-3.2311</v>
       </c>
       <c r="K16" t="n">
-        <v>0.03449999999999986</v>
+        <v>-0.4899999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.2311</v>
+        <v>-2.7412</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.822</v>
+        <v>-3.3476</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7924</v>
+        <v>-3.2631</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0296</v>
+        <v>-0.08460000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3964000000000004</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.9556</v>
+        <v>-4.9555</v>
       </c>
       <c r="R16" t="n">
-        <v>4.5592</v>
+        <v>4.9555</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9307</v>
+        <v>-2.7411</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.04000000000000004</v>
+        <v>-0.7365999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8907000000000002</v>
+        <v>-2.0045</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.8879</v>
+        <v>-0.5834999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.095000000000001</v>
+        <v>-0.5834999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. CABRERA RUIZ</t>
+          <t>D. NARANJO FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>-11.9967</v>
+        <v>-10.8855</v>
       </c>
       <c r="E17" t="n">
-        <v>-9.246599999999999</v>
+        <v>-7.1657</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.75</v>
+        <v>-3.7197</v>
       </c>
       <c r="G17" t="n">
-        <v>-10.7482</v>
+        <v>-6.0186</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.7829</v>
+        <v>-1.7579</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.9652</v>
+        <v>-4.2607</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.878400000000001</v>
+        <v>-3.1965</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.8605</v>
+        <v>0.03449999999999986</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.0179</v>
+        <v>-3.2311</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.8697</v>
+        <v>-2.822</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.9226</v>
+        <v>-1.7924</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.9473</v>
+        <v>-1.0296</v>
       </c>
       <c r="P17" t="n">
-        <v>6.3431</v>
+        <v>-0.3964000000000004</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.1448</v>
+        <v>-4.9556</v>
       </c>
       <c r="R17" t="n">
-        <v>12.488</v>
+        <v>4.5592</v>
       </c>
       <c r="S17" t="n">
-        <v>-7.2328</v>
+        <v>-0.5826</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4969</v>
+        <v>-0.2208</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.7358</v>
+        <v>-0.3618</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3591</v>
+        <v>-3.8879</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2734</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6325</v>
+        <v>-5.095000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D18" t="n">
-        <v>-13.1306</v>
+        <v>-12.2364</v>
       </c>
       <c r="E18" t="n">
-        <v>-22.7013</v>
+        <v>-5.922999999999998</v>
       </c>
       <c r="F18" t="n">
-        <v>9.5709</v>
+        <v>-6.3134</v>
       </c>
       <c r="G18" t="n">
-        <v>-7.674199999999999</v>
+        <v>-1.687100000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.124699999999999</v>
+        <v>-1.4635</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.5492</v>
+        <v>-0.2235999999999994</v>
       </c>
       <c r="J18" t="n">
-        <v>15.1139</v>
+        <v>30.1995</v>
       </c>
       <c r="K18" t="n">
-        <v>9.385400000000001</v>
+        <v>15.6639</v>
       </c>
       <c r="L18" t="n">
-        <v>5.7288</v>
+        <v>14.5355</v>
       </c>
       <c r="M18" t="n">
-        <v>-22.7879</v>
+        <v>-31.8868</v>
       </c>
       <c r="N18" t="n">
-        <v>-12.5105</v>
+        <v>-17.1277</v>
       </c>
       <c r="O18" t="n">
-        <v>-10.2776</v>
+        <v>-14.7591</v>
       </c>
       <c r="P18" t="n">
-        <v>-26.3638</v>
+        <v>7.5325</v>
       </c>
       <c r="Q18" t="n">
-        <v>-69.1798</v>
+        <v>-36.6711</v>
       </c>
       <c r="R18" t="n">
-        <v>42.8163</v>
+        <v>44.2039</v>
       </c>
       <c r="S18" t="n">
-        <v>33.0217</v>
+        <v>-6.7302</v>
       </c>
       <c r="T18" t="n">
-        <v>25.7262</v>
+        <v>-5.1345</v>
       </c>
       <c r="U18" t="n">
-        <v>7.2955</v>
+        <v>-1.5953</v>
       </c>
       <c r="V18" t="n">
-        <v>-12.1143</v>
+        <v>-11.3518</v>
       </c>
       <c r="W18" t="n">
-        <v>5.638199999999999</v>
+        <v>5.6834</v>
       </c>
       <c r="X18" t="n">
-        <v>-17.7529</v>
+        <v>-17.0354</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>-19.9269</v>
+        <v>-17.403</v>
       </c>
       <c r="E19" t="n">
-        <v>-11.9041</v>
+        <v>-10.2743</v>
       </c>
       <c r="F19" t="n">
-        <v>-8.0227</v>
+        <v>-7.1289</v>
       </c>
       <c r="G19" t="n">
         <v>-5.6781</v>
@@ -1936,13 +1936,13 @@
         <v>8.3253</v>
       </c>
       <c r="S19" t="n">
-        <v>-8.920999999999999</v>
+        <v>-6.3973</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.2503</v>
+        <v>-2.6203</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.6709</v>
+        <v>-3.7769</v>
       </c>
       <c r="V19" t="n">
         <v>-3.7421</v>
@@ -1969,13 +1969,13 @@
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-22.3217</v>
+        <v>-27.3878</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.1441</v>
+        <v>-15.7615</v>
       </c>
       <c r="F20" t="n">
-        <v>-14.1774</v>
+        <v>-11.6259</v>
       </c>
       <c r="G20" t="n">
         <v>-13.7427</v>
@@ -2014,13 +2014,13 @@
         <v>28.5443</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6332</v>
+        <v>-3.4332</v>
       </c>
       <c r="T20" t="n">
-        <v>7.535399999999999</v>
+        <v>-0.08199999999999996</v>
       </c>
       <c r="U20" t="n">
-        <v>-5.902100000000001</v>
+        <v>-3.3512</v>
       </c>
       <c r="V20" t="n">
         <v>-14.1766</v>
@@ -2047,13 +2047,13 @@
         <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>-24.986</v>
+        <v>-28.0702</v>
       </c>
       <c r="E21" t="n">
-        <v>-22.5817</v>
+        <v>-26.0784</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4041</v>
+        <v>-1.9922</v>
       </c>
       <c r="G21" t="n">
         <v>-20.9328</v>
@@ -2092,13 +2092,13 @@
         <v>13.281</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3442</v>
+        <v>-0.7405</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9123</v>
+        <v>-0.5845</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5683</v>
+        <v>-0.1563999999999998</v>
       </c>
       <c r="V21" t="n">
         <v>-4.8112</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>J. RAMIREZ GUERRA-LIBRERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>-27.2423</v>
+        <v>-28.4638</v>
       </c>
       <c r="E22" t="n">
-        <v>-18.574</v>
+        <v>-20.0686</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.668100000000001</v>
+        <v>-8.395200000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.687100000000001</v>
+        <v>-11.5879</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4635</v>
+        <v>-5.5783</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2235999999999994</v>
+        <v>-6.0096</v>
       </c>
       <c r="J22" t="n">
-        <v>30.1995</v>
+        <v>-3.7685</v>
       </c>
       <c r="K22" t="n">
-        <v>15.6639</v>
+        <v>-1.1479</v>
       </c>
       <c r="L22" t="n">
-        <v>14.5355</v>
+        <v>-2.6207</v>
       </c>
       <c r="M22" t="n">
-        <v>-31.8868</v>
+        <v>-7.8195</v>
       </c>
       <c r="N22" t="n">
-        <v>-17.1277</v>
+        <v>-4.430499999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-14.7591</v>
+        <v>-3.3891</v>
       </c>
       <c r="P22" t="n">
-        <v>7.5325</v>
+        <v>-7.1361</v>
       </c>
       <c r="Q22" t="n">
-        <v>-36.6711</v>
+        <v>-16.056</v>
       </c>
       <c r="R22" t="n">
-        <v>44.2039</v>
+        <v>8.92</v>
       </c>
       <c r="S22" t="n">
-        <v>-21.7356</v>
+        <v>-4.4627</v>
       </c>
       <c r="T22" t="n">
-        <v>-17.7856</v>
+        <v>-1.451</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.9498</v>
+        <v>-3.0119</v>
       </c>
       <c r="V22" t="n">
-        <v>-11.3518</v>
+        <v>-5.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>5.6834</v>
+        <v>1.2071</v>
       </c>
       <c r="X22" t="n">
-        <v>-17.0354</v>
+        <v>-6.4843</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RAMIREZ GUERRA-LIBRERO</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,70 +2200,70 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
-        <v>-29.8437</v>
+        <v>-36.0208</v>
       </c>
       <c r="E23" t="n">
-        <v>-20.5218</v>
+        <v>-41.104</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.3218</v>
+        <v>5.083399999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-11.5879</v>
+        <v>-7.674199999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.5783</v>
+        <v>-3.124699999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-6.0096</v>
+        <v>-4.5492</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.7685</v>
+        <v>15.1139</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1479</v>
+        <v>9.385400000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6207</v>
+        <v>5.7288</v>
       </c>
       <c r="M23" t="n">
-        <v>-7.8195</v>
+        <v>-22.7879</v>
       </c>
       <c r="N23" t="n">
-        <v>-4.430499999999999</v>
+        <v>-12.5105</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.3891</v>
+        <v>-10.2776</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.1361</v>
+        <v>-26.3638</v>
       </c>
       <c r="Q23" t="n">
-        <v>-16.056</v>
+        <v>-69.1798</v>
       </c>
       <c r="R23" t="n">
-        <v>8.92</v>
+        <v>42.8163</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.8426</v>
+        <v>10.1315</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.9043</v>
+        <v>7.323399999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.9384</v>
+        <v>2.8079</v>
       </c>
       <c r="V23" t="n">
-        <v>-5.2772</v>
+        <v>-12.1143</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2071</v>
+        <v>5.638199999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.4843</v>
+        <v>-17.7529</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>-38.6656</v>
+        <v>-36.1519</v>
       </c>
       <c r="E24" t="n">
-        <v>-39.0232</v>
+        <v>-36.9729</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3578000000000003</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-2.365</v>
@@ -2326,13 +2326,13 @@
         <v>37.4644</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.043999999999999</v>
+        <v>-6.5305</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.5509</v>
+        <v>-3.5008</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.4935</v>
+        <v>-3.0297</v>
       </c>
       <c r="V24" t="n">
         <v>-17.9395</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. MONTIEL RODRIGUEZ</t>
+          <t>E. LOPEZ GARCIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2356,76 +2356,76 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
-        <v>-48.1319</v>
+        <v>-41.8</v>
       </c>
       <c r="E25" t="n">
-        <v>-40.3403</v>
+        <v>-37.4491</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.791700000000001</v>
+        <v>-4.350299999999998</v>
       </c>
       <c r="G25" t="n">
-        <v>-26.381</v>
+        <v>-23.2772</v>
       </c>
       <c r="H25" t="n">
-        <v>-17.3146</v>
+        <v>-25.6254</v>
       </c>
       <c r="I25" t="n">
-        <v>-9.0662</v>
+        <v>2.3483</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.6866</v>
+        <v>-3.357900000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.7566</v>
+        <v>-10.0212</v>
       </c>
       <c r="L25" t="n">
-        <v>0.07020000000000014</v>
+        <v>6.6631</v>
       </c>
       <c r="M25" t="n">
-        <v>-21.6943</v>
+        <v>-19.9192</v>
       </c>
       <c r="N25" t="n">
-        <v>-12.5585</v>
+        <v>-15.6043</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.1363</v>
+        <v>-4.3146</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.7752</v>
+        <v>-5.1537</v>
       </c>
       <c r="Q25" t="n">
-        <v>-34.2925</v>
+        <v>-31.3191</v>
       </c>
       <c r="R25" t="n">
-        <v>31.5176</v>
+        <v>26.1655</v>
       </c>
       <c r="S25" t="n">
-        <v>-11.9577</v>
+        <v>-9.144</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.8929</v>
+        <v>-5.5635</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.0648</v>
+        <v>-3.5803</v>
       </c>
       <c r="V25" t="n">
-        <v>-7.0181</v>
+        <v>-4.224799999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>4.5318</v>
+        <v>2.7916</v>
       </c>
       <c r="X25" t="n">
-        <v>-11.5502</v>
+        <v>-7.0164</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E. LOPEZ GARCIA</t>
+          <t>F. MONTIEL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2434,70 +2434,70 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>-50.3349</v>
+        <v>-43.0012</v>
       </c>
       <c r="E26" t="n">
-        <v>-43.6302</v>
+        <v>-36.5813</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.704400000000001</v>
+        <v>-6.419499999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-23.2772</v>
+        <v>-26.381</v>
       </c>
       <c r="H26" t="n">
-        <v>-25.6254</v>
+        <v>-17.3146</v>
       </c>
       <c r="I26" t="n">
-        <v>2.3483</v>
+        <v>-9.0662</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.357900000000001</v>
+        <v>-4.6866</v>
       </c>
       <c r="K26" t="n">
-        <v>-10.0212</v>
+        <v>-4.7566</v>
       </c>
       <c r="L26" t="n">
-        <v>6.6631</v>
+        <v>0.07020000000000014</v>
       </c>
       <c r="M26" t="n">
-        <v>-19.9192</v>
+        <v>-21.6943</v>
       </c>
       <c r="N26" t="n">
-        <v>-15.6043</v>
+        <v>-12.5585</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.3146</v>
+        <v>-9.1363</v>
       </c>
       <c r="P26" t="n">
-        <v>-5.1537</v>
+        <v>-2.7752</v>
       </c>
       <c r="Q26" t="n">
-        <v>-31.3191</v>
+        <v>-34.2925</v>
       </c>
       <c r="R26" t="n">
-        <v>26.1655</v>
+        <v>31.5176</v>
       </c>
       <c r="S26" t="n">
-        <v>-17.6789</v>
+        <v>-6.8267</v>
       </c>
       <c r="T26" t="n">
-        <v>-11.7447</v>
+        <v>-2.1337</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.9346</v>
+        <v>-4.6928</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.224799999999999</v>
+        <v>-7.0181</v>
       </c>
       <c r="W26" t="n">
-        <v>2.7916</v>
+        <v>4.5318</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.0164</v>
+        <v>-11.5502</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>23</v>
       </c>
       <c r="D27" t="n">
-        <v>-52.4769</v>
+        <v>-60.5729</v>
       </c>
       <c r="E27" t="n">
-        <v>-34.4832</v>
+        <v>-40.3101</v>
       </c>
       <c r="F27" t="n">
-        <v>-17.9939</v>
+        <v>-20.2628</v>
       </c>
       <c r="G27" t="n">
         <v>-30.9216</v>
@@ -2560,13 +2560,13 @@
         <v>37.8606</v>
       </c>
       <c r="S27" t="n">
-        <v>5.3649</v>
+        <v>-2.7312</v>
       </c>
       <c r="T27" t="n">
-        <v>7.0736</v>
+        <v>1.2468</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.7089</v>
+        <v>-3.978</v>
       </c>
       <c r="V27" t="n">
         <v>-13.6392</v>
@@ -2593,13 +2593,13 @@
         <v>25</v>
       </c>
       <c r="D28" t="n">
-        <v>-383.6442</v>
+        <v>-367.7504</v>
       </c>
       <c r="E28" t="n">
-        <v>-317.9875</v>
+        <v>-309.564</v>
       </c>
       <c r="F28" t="n">
-        <v>-65.6557</v>
+        <v>-58.1851</v>
       </c>
       <c r="G28" t="n">
         <v>-158.6817</v>
@@ -2614,10 +2614,10 @@
         <v>105.1447</v>
       </c>
       <c r="K28" t="n">
-        <v>61.37819999999999</v>
+        <v>61.37820000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>43.76690000000001</v>
+        <v>43.76689999999999</v>
       </c>
       <c r="M28" t="n">
         <v>-263.8262</v>
@@ -2626,7 +2626,7 @@
         <v>-175.026</v>
       </c>
       <c r="O28" t="n">
-        <v>-88.80119999999999</v>
+        <v>-88.80120000000001</v>
       </c>
       <c r="P28" t="n">
         <v>-58.4764</v>
@@ -2638,16 +2638,16 @@
         <v>425.1895</v>
       </c>
       <c r="S28" t="n">
-        <v>-73.54320000000001</v>
+        <v>-57.6509</v>
       </c>
       <c r="T28" t="n">
-        <v>-33.5879</v>
+        <v>-25.164</v>
       </c>
       <c r="U28" t="n">
-        <v>-39.9572</v>
+        <v>-32.4873</v>
       </c>
       <c r="V28" t="n">
-        <v>-92.9418</v>
+        <v>-92.94180000000001</v>
       </c>
       <c r="W28" t="n">
         <v>94.12010000000001</v>
